--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T13:30:57+00:00</t>
+    <t>2023-04-28T11:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T11:34:44+00:00</t>
+    <t>2023-04-30T04:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-30T04:59:44+00:00</t>
+    <t>2023-05-01T18:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-01T18:23:44+00:00</t>
+    <t>2023-05-03T04:38:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-03T04:38:57+00:00</t>
+    <t>2023-05-04T06:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T06:27:52+00:00</t>
+    <t>2023-05-05T18:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:20+00:00</t>
+    <t>2023-05-05T18:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:27:53+00:00</t>
+    <t>2023-05-05T20:52:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:52:16+00:00</t>
+    <t>2023-05-06T12:19:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1397,44 +1397,45 @@
 </t>
   </si>
   <si>
+    <t>dateTime
+PeriodTiming</t>
+  </si>
+  <si>
+    <t>When service should occur</t>
+  </si>
+  <si>
+    <t>The date/time at which the requested service should occur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>TQ1/TQ2, OBR-7/OBR-8</t>
+  </si>
+  <si>
+    <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>FiveWs.planned</t>
+  </si>
+  <si>
+    <t>Procedure.procedureSchedule</t>
+  </si>
+  <si>
+    <t>ServiceRequest.occurrence[x]:occurrenceDateTime</t>
+  </si>
+  <si>
+    <t>occurrenceDateTime</t>
+  </si>
+  <si>
     <t xml:space="preserve">dateTime
 </t>
   </si>
   <si>
-    <t>When service should occur</t>
-  </si>
-  <si>
-    <t>The date/time at which the requested service should occur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Request.occurrence[x]</t>
-  </si>
-  <si>
-    <t>TQ1/TQ2, OBR-7/OBR-8</t>
-  </si>
-  <si>
-    <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.planned</t>
-  </si>
-  <si>
-    <t>Procedure.procedureSchedule</t>
-  </si>
-  <si>
-    <t>ServiceRequest.occurrence[x]:occurrenceDateTime</t>
-  </si>
-  <si>
-    <t>occurrenceDateTime</t>
-  </si>
-  <si>
     <t>ServiceRequest.asNeeded[x]</t>
   </si>
   <si>
@@ -1629,7 +1630,7 @@
     <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-for-assessment-or-test-not-performed</t>
+    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-for-assessment</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1656,7 +1657,7 @@
     <t>ServiceRequest.reasonCode.text</t>
   </si>
   <si>
-    <t>Reason</t>
+    <t>Reason for testing</t>
   </si>
   <si>
     <t>ServiceRequest.reasonReference</t>
@@ -2185,7 +2186,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="126.34765625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="85.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3510,13 +3511,13 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>81</v>
@@ -5507,13 +5508,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>81</v>
@@ -8079,7 +8080,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>89</v>
@@ -8146,7 +8147,7 @@
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>451</v>
+        <v>173</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>445</v>
@@ -8164,43 +8165,43 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL51" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AM51" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO51" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>445</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>446</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
@@ -8209,7 +8210,7 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>448</v>
@@ -8281,19 +8282,19 @@
         <v>101</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AL52" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>456</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -8439,7 +8440,7 @@
         <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>469</v>
@@ -8776,7 +8777,7 @@
         <v>89</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$86</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2700" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3213" uniqueCount="633">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -240,13 +240,13 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
-    <t>Mapping: HL7 v2 Mapping</t>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
     <t>Mapping: Quality Improvement and Clinical Knowledge (QUICK)</t>
@@ -278,10 +278,13 @@
     <t>Request</t>
   </si>
   <si>
+    <t>clinical.general</t>
+  </si>
+  <si>
     <t>ORC</t>
   </si>
   <si>
-    <t>Act[moodCode&lt;=INT]</t>
+    <t>Entity, Role, or Act,Act[moodCode&lt;=INT]</t>
   </si>
   <si>
     <t>ServiceRequest.id</t>
@@ -303,7 +306,7 @@
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -342,7 +345,7 @@
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -364,13 +367,13 @@
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>IETF language tag for a human language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -393,10 +396,14 @@
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-6
+</t>
   </si>
   <si>
     <t>Act.text?</t>
@@ -416,13 +423,17 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
   </si>
   <si>
     <t>N/A</t>
@@ -442,7 +453,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
@@ -461,11 +472,11 @@
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -484,31 +495,31 @@
     <t>Identifiers assigned to this order instance by the orderer and/or the receiver and/or order fulfiller.</t>
   </si>
   <si>
-    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 v2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 v2).  For further discussion and examples see the resource notes section below.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:system}
+    <t>The identifier.type element is used to distinguish between the identifiers assigned by the orderer (known as the 'Placer' in HL7 V2) and the producer of the observations in response to the order (known as the 'Filler' in HL7 V2).  For further discussion and examples see the resource notes section below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
 </t>
   </si>
   <si>
-    <t>Slice based on the type of identifier</t>
-  </si>
-  <si>
-    <t>openAtEnd</t>
+    <t>Slice based on the type of identifier.</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>Request.identifier</t>
   </si>
   <si>
-    <t>ORC.2, ORC.3, RF1-6 / RF1-11,</t>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>ORC-2, ORC-3, RF1-6 / RF1-11,</t>
   </si>
   <si>
     <t>.identifier</t>
   </si>
   <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
     <t>ClinicalStatement.identifier</t>
   </si>
   <si>
@@ -522,241 +533,243 @@
   </si>
   <si>
     <t>ServiceRequest.identifier.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.use</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|5.0.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.system</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should be an absolute reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.version</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.version</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier:PLAC.type.coding.code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.identifier.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cod-1
 </t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.use</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.system</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.version</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier:PLAC.type.coding.code</t>
-  </si>
-  <si>
-    <t>ServiceRequest.identifier.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -862,7 +875,7 @@
     <t>The namespace for the identifier value</t>
   </si>
   <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Establishes the namespace for the value - that is, an absolute URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -898,13 +911,17 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [http://hl7.org/fhir/StructureDefinition/rendered-value](http://hl7.org/fhir/extensions/StructureDefinition-rendered-value.html)). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
   </si>
   <si>
     <t>Identifier.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ident-1
+</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -979,7 +996,7 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this ServiceRequest.</t>
   </si>
   <si>
-    <t>Note: This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and a Person resource instance might share the same social insurance number.</t>
+    <t>The PlanDefinition resource is used to describe series, sequences, or groups of actions to be taken, while the ActivityDefinition resource is used to define each specific step or activity to be performed. More information can be found in the [Boundaries and Relationships](http://hl7.org/fhir/R5/plandefinition.html#12.23.2) section for PlanDefinition.</t>
   </si>
   <si>
     <t>Request.instantiatesCanonical</t>
@@ -1026,7 +1043,7 @@
     <t>Request.basedOn</t>
   </si>
   <si>
-    <t>ORC.8 (plus others)</t>
+    <t>ORC-8 (plus others)</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=FLFS].target</t>
@@ -1052,7 +1069,7 @@
     <t>Request.replaces</t>
   </si>
   <si>
-    <t>Handled by message location of ORC (ORC.1=RO or RU)</t>
+    <t>Handled by message location of ORC (ORC-1=RO or RU)</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=RPLC].target</t>
@@ -1080,7 +1097,7 @@
     <t>Request.groupIdentifier</t>
   </si>
   <si>
-    <t>ORC.4</t>
+    <t>ORC-4</t>
   </si>
   <si>
     <t>.inboundRelationship(typeCode=COMP].source[moodCode=INT].identifier</t>
@@ -1095,34 +1112,34 @@
     <t>The status of the order.</t>
   </si>
   <si>
-    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, cancelled or suspended. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R4/task.html) resource.</t>
+    <t>The status is generally fully in the control of the requester - they determine whether the order is draft or active and, after it has been activated, competed, revoked or placed on-hold. States relating to the activities of the performer are reflected on either the corresponding event (see [Event Pattern](event.html) for general discussion) or using the [Task](http://hl7.org/fhir/R5/task.html) resource.</t>
   </si>
   <si>
     <t>The status of a service order.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-status|5.0.0</t>
   </si>
   <si>
     <t>Request.status</t>
   </si>
   <si>
-    <t>ORC.5,RF1-1</t>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>ORC-5,RF1-1</t>
   </si>
   <si>
     <t>.status</t>
   </si>
   <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
     <t>Action.currentStatus</t>
   </si>
   <si>
     <t>ServiceRequest.intent</t>
   </si>
   <si>
-    <t>proposal | plan | directive | order | original-order | reflex-order | filler-order | instance-order | option</t>
+    <t>proposal | plan | directive | order +</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, an original order or a reflex order.</t>
@@ -1137,18 +1154,18 @@
     <t>The kind of service request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-intent|5.0.0</t>
   </si>
   <si>
     <t>Request.intent</t>
   </si>
   <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
     <t>.moodCode (nuances beyond PRP/PLAN/RQO would need to be elsewhere)</t>
   </si>
   <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>ServiceRequest.category</t>
   </si>
   <si>
@@ -1194,19 +1211,19 @@
     <t>Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|5.0.0</t>
   </si>
   <si>
     <t>Request.priority</t>
   </si>
   <si>
+    <t>FiveWs.grade</t>
+  </si>
+  <si>
     <t>TQ1.9, RF1-2</t>
   </si>
   <si>
     <t>.priorityCode</t>
-  </si>
-  <si>
-    <t>FiveWs.grade</t>
   </si>
   <si>
     <t>ServiceRequest.doNotPerform</t>
@@ -1240,10 +1257,14 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">CodeableReference(ActivityDefinition|PlanDefinition)
+</t>
+  </si>
+  <si>
     <t>What is being requested/ordered</t>
   </si>
   <si>
-    <t>A code that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
+    <t>A code or reference that identifies a particular service (i.e., procedure, diagnostic investigation, or panel of investigations) that have been requested.</t>
   </si>
   <si>
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
@@ -1252,18 +1273,22 @@
     <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-test-types</t>
   </si>
   <si>
+    <t xml:space="preserve">prr-1
+</t>
+  </si>
+  <si>
     <t>Request.code</t>
   </si>
   <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
     <t>PR1-3 / OBR-4  (varies by domain)</t>
   </si>
   <si>
     <t>.code</t>
   </si>
   <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>Procedure.procedureCode</t>
   </si>
   <si>
@@ -1273,13 +1298,47 @@
     <t>ServiceRequest.code.extension</t>
   </si>
   <si>
-    <t>ServiceRequest.code.coding</t>
-  </si>
-  <si>
-    <t>ServiceRequest.code.text</t>
+    <t>ServiceRequest.code.concept</t>
+  </si>
+  <si>
+    <t>Reference to a concept (by class)</t>
+  </si>
+  <si>
+    <t>A reference to a concept - e.g. the information is identified by its general class to the degree of precision found in the terminology.</t>
+  </si>
+  <si>
+    <t>CodeableReference.concept</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.concept.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.concept.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.concept.coding</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.concept.text</t>
   </si>
   <si>
     <t>Test Type</t>
+  </si>
+  <si>
+    <t>ServiceRequest.code.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference
+</t>
+  </si>
+  <si>
+    <t>Reference to a resource (by instance)</t>
+  </si>
+  <si>
+    <t>A reference to a resource the provides exact details about the information being referenced.</t>
+  </si>
+  <si>
+    <t>CodeableReference.reference</t>
   </si>
   <si>
     <t>ServiceRequest.orderDetail</t>
@@ -1289,6 +1348,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
     <t>Additional order information</t>
   </si>
   <si>
@@ -1298,17 +1361,92 @@
     <t>For information from the medical record intended to support the delivery of the requested services, use the `supportingInformation` element.</t>
   </si>
   <si>
-    <t>Codified order entry details which are based on order context.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prr-1
+    <t>NTE</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameterFocus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableReference(Device|DeviceDefinition|DeviceRequest|SupplyRequest|Medication|MedicationRequest|BiologicallyDerivedProduct|Substance)
 </t>
   </si>
   <si>
-    <t>NTE</t>
+    <t>The context of the order details by reference</t>
+  </si>
+  <si>
+    <t>Indicates the context of the order details by reference.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter</t>
+  </si>
+  <si>
+    <t>The parameter details for the service being requested</t>
+  </si>
+  <si>
+    <t>The parameter details for the service being requested.</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter.modifierExtension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter.code</t>
+  </si>
+  <si>
+    <t>The detail of the order being requested</t>
+  </si>
+  <si>
+    <t>A value representing the additional detail or instructions for the order (e.g., catheter insertion, body elevation, descriptive device configuration and/or setting instructions).</t>
+  </si>
+  <si>
+    <t>Codes for order detail parameters.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail-parameter-code</t>
+  </si>
+  <si>
+    <t>ServiceRequest.orderDetail.parameter.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+RatioRangebooleanCodeableConceptstringPeriod</t>
+  </si>
+  <si>
+    <t>The value for the order detail</t>
+  </si>
+  <si>
+    <t>Indicates a value for the order detail.</t>
+  </si>
+  <si>
+    <t>CodeableConcept values are indented to express concepts that would normally be coded - when a code is not available for a concept, CodeableConcept.text can be used. When the data is a text or not a single identifiable concept, string should be used.</t>
   </si>
   <si>
     <t>ServiceRequest.quantity[x]</t>
@@ -1346,16 +1484,32 @@
     <t>Request.subject</t>
   </si>
   <si>
+    <t>FiveWs.subject[x]</t>
+  </si>
+  <si>
     <t>PID</t>
   </si>
   <si>
     <t>.participation[typeCode=SBJ].role</t>
   </si>
   <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
     <t>ClinicalStatement.subject</t>
+  </si>
+  <si>
+    <t>ServiceRequest.focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Resource)
+</t>
+  </si>
+  <si>
+    <t>What the service request is about, when it is not about the subject of record</t>
+  </si>
+  <si>
+    <t>The actual focus of a service request when it is not the subject of record representing something or someone associated with the subject such as a spouse, parent, fetus, or donor. The focus of a service request could also be an existing condition,  an intervention, the subject's diet,  another service request on the subject,  or a body structure such as tumor or implanted device.</t>
+  </si>
+  <si>
+    <t>participation[typeCode=SBJ]</t>
   </si>
   <si>
     <t>ServiceRequest.encounter</t>
@@ -1378,13 +1532,13 @@
     <t>Request.encounter</t>
   </si>
   <si>
+    <t>FiveWs.context</t>
+  </si>
+  <si>
     <t>PV1</t>
   </si>
   <si>
     <t>.inboundRelationship(typeCode=COMP].source[classCode&lt;=PCPR, moodCode=EVN]</t>
-  </si>
-  <si>
-    <t>FiveWs.context</t>
   </si>
   <si>
     <t>ClinicalStatement.encounter</t>
@@ -1414,13 +1568,13 @@
     <t>Request.occurrence[x]</t>
   </si>
   <si>
+    <t>FiveWs.planned</t>
+  </si>
+  <si>
     <t>TQ1/TQ2, OBR-7/OBR-8</t>
   </si>
   <si>
     <t>.effectiveTime</t>
-  </si>
-  <si>
-    <t>FiveWs.planned</t>
   </si>
   <si>
     <t>Procedure.procedureSchedule</t>
@@ -1477,13 +1631,13 @@
     <t>Request.authoredOn</t>
   </si>
   <si>
-    <t>ORC.9,  RF1-7 / RF1-9</t>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>ORC-9,  RF1-7 / RF1-9</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
   </si>
   <si>
     <t>Proposal.proposedAtTime</t>
@@ -1512,13 +1666,13 @@
     <t>Request.requester</t>
   </si>
   <si>
-    <t>ORC.12, PRT</t>
+    <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>ORC-12, PRT</t>
   </si>
   <si>
     <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.author</t>
   </si>
   <si>
     <t>ClinicalStatement.statementAuthor</t>
@@ -1549,13 +1703,13 @@
     <t>Request.performerType</t>
   </si>
   <si>
-    <t>PRT, RF!-3</t>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>PRT, RF1-3</t>
   </si>
   <si>
     <t>.participation[typeCode=PRF].role[scoper.determinerCode=KIND].code</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>ServiceRequest.performer</t>
@@ -1575,7 +1729,7 @@
     <t>The desired performer for doing the requested service.  For example, the surgeon, dermatopathologist, endoscopist, etc.</t>
   </si>
   <si>
-    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [request-performerOrder extension](http://hl7.org/fhir/R4/extension-request-performerorder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
+    <t>If multiple performers are present, it is interpreted as a list of *alternative* performers without any preference regardless of order.  If order of preference is needed use the [http://hl7.org/fhir/StructureDefinition/request-performerOrder](http://hl7.org/fhir/extensions/StructureDefinition-request-performerOrder.html).  Use CareTeam to represent a group of performers (for example, Practitioner A *and* Practitioner B).</t>
   </si>
   <si>
     <t>Request.performer</t>
@@ -1587,7 +1741,11 @@
     <t>.participation[typeCode=PRF].role[scoper.determinerCode=INSTANCE]</t>
   </si>
   <si>
-    <t>ServiceRequest.locationCode</t>
+    <t>ServiceRequest.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableReference(Location)
+</t>
   </si>
   <si>
     <t>Requested location</t>
@@ -1605,84 +1763,38 @@
     <t>.participation[typeCode=LOC].role[scoper.determinerCode=KIND].code</t>
   </si>
   <si>
-    <t>ServiceRequest.locationReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location)
+    <t>ServiceRequest.reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableReference(Observation)
 </t>
   </si>
   <si>
-    <t>A reference to the the preferred location(s) where the procedure should actually happen. E.g. at home or nursing day care center.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=LOC].role[scoper.determinerCode=INSTANCE]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode</t>
-  </si>
-  <si>
     <t>Explanation/Justification for procedure or service</t>
   </si>
   <si>
     <t>An explanation or justification for why this service is being requested in coded or textual form.   This is often for billing purposes.  May relate to the resources referred to in `supportingInfo`.</t>
   </si>
   <si>
-    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.   Use `CodeableConcept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
-  </si>
-  <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-reason-for-assessment</t>
-  </si>
-  <si>
-    <t>Request.reasonCode</t>
-  </si>
-  <si>
-    <t>ORC.16, RF1-10</t>
+    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all. To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise, use `concept.text` element if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
+  </si>
+  <si>
+    <t>SNOMED CT Condition/Problem/Diagnosis Codes</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+  </si>
+  <si>
+    <t>Request.reason</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>ORC-16, RF1-10</t>
   </si>
   <si>
     <t>.reasonCode</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode.id</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode.extension</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode.coding</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonCode.text</t>
-  </si>
-  <si>
-    <t>Reason for testing</t>
-  </si>
-  <si>
-    <t>ServiceRequest.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
-</t>
-  </si>
-  <si>
-    <t>Explanation/Justification for service or service</t>
-  </si>
-  <si>
-    <t>Indicates another resource that provides a justification for why this service is being requested.   May relate to the resources referred to in `supportingInfo`.</t>
-  </si>
-  <si>
-    <t>This element represents why the referral is being made and may be used to decide how the service will be performed, or even if it will be performed at all.    To be as specific as possible,  a reference to  *Observation* or *Condition* should be used if available.  Otherwise when referencing  *DiagnosticReport*  it should contain a finding  in `DiagnosticReport.conclusion` and/or `DiagnosticReport.conclusionCode`.   When using a reference to *DocumentReference*, the target document should contain clear findings language providing the relevant reason for this service request.  Use  the CodeableConcept text element in `ServiceRequest.reasonCode` if the data is free (uncoded) text as shown in the [CT Scan example](servicerequest-example-di.html).</t>
-  </si>
-  <si>
-    <t>Request.reasonReference</t>
-  </si>
-  <si>
-    <t>ORC.16</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode=RSON].target</t>
   </si>
   <si>
     <t>ServiceRequest.insurance</t>
@@ -1714,7 +1826,7 @@
 AOE</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">CodeableReference(Resource)
 </t>
   </si>
   <si>
@@ -1749,7 +1861,7 @@
     <t>One or more specimens that the laboratory procedure will use.</t>
   </si>
   <si>
-    <t>Many diagnostic procedures need a specimen, but the request itself is not actually about the specimen. This element is for when the diagnostic is requested on already existing specimens and the request points to the specimen it applies to.    Conversely, if the request is entered first with an unknown specimen, then the [Specimen](http://hl7.org/fhir/R4/specimen.html) resource points to the ServiceRequest.</t>
+    <t>The purpose of the ServiceRequest.specimen is to reflect the actual specimen that the requested test/procedure is asked to be performed on, whether the lab already has it or not.  References to specimens for purposes other than to perform a test/procedure on should be made using the ServiceRequest.supportingInfo or the Specimen.parent where the Specimen.parent would enable descendency and ServiceRequest.supportingInfo a general reference for context.</t>
   </si>
   <si>
     <t>SPM</t>
@@ -1765,28 +1877,49 @@
 </t>
   </si>
   <si>
-    <t>Location on Body</t>
+    <t>Coded location on Body</t>
   </si>
   <si>
     <t>Anatomic location where the procedure should be performed. This is the target site.</t>
   </si>
   <si>
-    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [procedure-targetBodyStructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
+    <t>Only used if not implicit in the code found in ServiceRequest.code.  If the use case requires BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [http://hl7.org/fhir/StructureDefinition/procedure-targetBodyStructure](http://hl7.org/fhir/extensions/StructureDefinition-procedure-targetBodyStructure.html).</t>
   </si>
   <si>
     <t>Knowing where the procedure is performed is important for tracking if multiple sites are possible.</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
+    <t xml:space="preserve">bdystr-1
+</t>
+  </si>
+  <si>
     <t>targetSiteCode</t>
   </si>
   <si>
     <t>Procedure.targetBodySite</t>
+  </si>
+  <si>
+    <t>ServiceRequest.bodyStructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locationStructure
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(BodyStructure)
+</t>
+  </si>
+  <si>
+    <t>BodyStructure-based location on the body</t>
+  </si>
+  <si>
+    <t>Procedure.targetBodyStructure</t>
   </si>
   <si>
     <t>ServiceRequest.note</t>
@@ -1818,6 +1951,22 @@
   </si>
   <si>
     <t>.text</t>
+  </si>
+  <si>
+    <t>ServiceRequest.patientInstruction.id</t>
+  </si>
+  <si>
+    <t>ServiceRequest.patientInstruction.extension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.patientInstruction.modifierExtension</t>
+  </si>
+  <si>
+    <t>ServiceRequest.patientInstruction.instruction[x]</t>
+  </si>
+  <si>
+    <t>markdown
+Reference(DocumentReference)</t>
   </si>
   <si>
     <t>ServiceRequest.relevantHistory</t>
@@ -1990,7 +2139,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -2077,77 +2226,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -2158,11 +2315,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO72"/>
+  <dimension ref="A1:AO86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.35546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.71484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="53.71484375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="20.203125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="44.00390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -2171,7 +2328,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="105.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="135.5703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2192,14 +2349,14 @@
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.71484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.1484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="85.41796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="163.4453125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="85.41796875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="163.4453125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="66.88671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2437,7 +2594,7 @@
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="AO2" t="s" s="2">
         <v>81</v>
@@ -2445,10 +2602,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2459,7 +2616,7 @@
         <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>81</v>
@@ -2468,19 +2625,19 @@
         <v>81</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2530,13 +2687,13 @@
         <v>81</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>81</v>
@@ -2562,10 +2719,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2576,7 +2733,7 @@
         <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>81</v>
@@ -2585,16 +2742,16 @@
         <v>81</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2645,19 +2802,19 @@
         <v>81</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>81</v>
@@ -2677,10 +2834,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2691,28 +2848,28 @@
         <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2762,19 +2919,19 @@
         <v>81</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>81</v>
@@ -2794,10 +2951,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2808,7 +2965,7 @@
         <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>81</v>
@@ -2820,16 +2977,16 @@
         <v>81</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2855,13 +3012,13 @@
         <v>81</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>81</v>
@@ -2879,19 +3036,19 @@
         <v>81</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>81</v>
@@ -2911,21 +3068,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>81</v>
@@ -2937,16 +3094,16 @@
         <v>81</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2996,19 +3153,19 @@
         <v>81</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>81</v>
@@ -3017,10 +3174,10 @@
         <v>81</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>81</v>
@@ -3028,14 +3185,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -3054,16 +3211,16 @@
         <v>81</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3113,7 +3270,7 @@
         <v>81</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>79</v>
@@ -3122,7 +3279,7 @@
         <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>81</v>
@@ -3134,10 +3291,10 @@
         <v>81</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>81</v>
@@ -3145,14 +3302,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3171,16 +3328,16 @@
         <v>81</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3230,7 +3387,7 @@
         <v>81</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>79</v>
@@ -3242,7 +3399,7 @@
         <v>81</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>81</v>
@@ -3251,10 +3408,10 @@
         <v>81</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>81</v>
@@ -3262,14 +3419,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3282,25 +3439,25 @@
         <v>81</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>81</v>
@@ -3349,7 +3506,7 @@
         <v>81</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>79</v>
@@ -3361,7 +3518,7 @@
         <v>81</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>81</v>
@@ -3370,10 +3527,10 @@
         <v>81</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>81</v>
@@ -3381,10 +3538,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3392,7 +3549,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>80</v>
@@ -3404,19 +3561,19 @@
         <v>81</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3454,19 +3611,19 @@
         <v>81</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -3478,33 +3635,33 @@
         <v>81</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>81</v>
@@ -3514,28 +3671,28 @@
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3585,7 +3742,7 @@
         <v>81</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -3597,30 +3754,30 @@
         <v>81</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3631,7 +3788,7 @@
         <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>81</v>
@@ -3643,13 +3800,13 @@
         <v>81</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3700,16 +3857,16 @@
         <v>81</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>81</v>
@@ -3721,10 +3878,10 @@
         <v>81</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>81</v>
@@ -3732,14 +3889,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3758,16 +3915,16 @@
         <v>81</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3805,19 +3962,19 @@
         <v>81</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -3829,7 +3986,7 @@
         <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>81</v>
@@ -3838,10 +3995,10 @@
         <v>81</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>81</v>
@@ -3849,10 +4006,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3863,31 +4020,31 @@
         <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>81</v>
@@ -3912,13 +4069,13 @@
         <v>81</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>81</v>
@@ -3936,31 +4093,31 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>81</v>
@@ -3968,10 +4125,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3982,7 +4139,7 @@
         <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>81</v>
@@ -3991,22 +4148,22 @@
         <v>81</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>81</v>
@@ -4031,13 +4188,13 @@
         <v>81</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>81</v>
@@ -4055,31 +4212,31 @@
         <v>81</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>81</v>
@@ -4087,10 +4244,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4101,7 +4258,7 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>81</v>
@@ -4113,13 +4270,13 @@
         <v>81</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4170,16 +4327,16 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>81</v>
@@ -4191,10 +4348,10 @@
         <v>81</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>81</v>
@@ -4202,14 +4359,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4228,16 +4385,16 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4275,19 +4432,19 @@
         <v>81</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4299,7 +4456,7 @@
         <v>81</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>81</v>
@@ -4308,10 +4465,10 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>81</v>
@@ -4319,10 +4476,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4342,22 +4499,22 @@
         <v>81</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>81</v>
@@ -4406,7 +4563,7 @@
         <v>81</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4418,19 +4575,19 @@
         <v>81</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>211</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>81</v>
@@ -4438,10 +4595,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4452,7 +4609,7 @@
         <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>81</v>
@@ -4464,13 +4621,13 @@
         <v>81</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4521,16 +4678,16 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>81</v>
@@ -4542,10 +4699,10 @@
         <v>81</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>81</v>
@@ -4553,14 +4710,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4579,16 +4736,16 @@
         <v>81</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4626,19 +4783,19 @@
         <v>81</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4650,7 +4807,7 @@
         <v>81</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>81</v>
@@ -4659,10 +4816,10 @@
         <v>81</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>81</v>
@@ -4670,10 +4827,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4684,7 +4841,7 @@
         <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>81</v>
@@ -4693,22 +4850,22 @@
         <v>81</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4718,7 +4875,7 @@
         <v>81</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>81</v>
@@ -4757,31 +4914,31 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>81</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>81</v>
@@ -4789,10 +4946,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4803,7 +4960,7 @@
         <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>81</v>
@@ -4812,19 +4969,19 @@
         <v>81</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4874,31 +5031,31 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>81</v>
+        <v>235</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>81</v>
@@ -4906,10 +5063,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4920,7 +5077,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>81</v>
@@ -4929,20 +5086,20 @@
         <v>81</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4952,7 +5109,7 @@
         <v>81</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>81</v>
@@ -4991,31 +5148,31 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>81</v>
+        <v>242</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>81</v>
@@ -5023,10 +5180,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5037,7 +5194,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>81</v>
@@ -5046,20 +5203,20 @@
         <v>81</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -5069,7 +5226,7 @@
         <v>81</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>81</v>
@@ -5108,31 +5265,31 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>81</v>
+        <v>242</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>249</v>
+        <v>81</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>81</v>
+        <v>253</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>81</v>
@@ -5140,10 +5297,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5154,7 +5311,7 @@
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>81</v>
@@ -5163,22 +5320,22 @@
         <v>81</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>81</v>
@@ -5227,31 +5384,31 @@
         <v>81</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>81</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>81</v>
+        <v>263</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>81</v>
@@ -5259,10 +5416,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5273,7 +5430,7 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>81</v>
@@ -5282,22 +5439,22 @@
         <v>81</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>81</v>
@@ -5307,7 +5464,7 @@
         <v>81</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>81</v>
@@ -5346,31 +5503,31 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>81</v>
+        <v>273</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>81</v>
@@ -5378,10 +5535,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5389,10 +5546,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>81</v>
@@ -5401,35 +5558,35 @@
         <v>81</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>81</v>
@@ -5465,31 +5622,31 @@
         <v>81</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>280</v>
+        <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>81</v>
+        <v>284</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>81</v>
@@ -5497,10 +5654,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5511,28 +5668,28 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>163</v>
+        <v>229</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5546,7 +5703,7 @@
         <v>81</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>81</v>
@@ -5582,31 +5739,31 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>289</v>
+        <v>81</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>81</v>
+        <v>294</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>81</v>
@@ -5614,10 +5771,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5628,7 +5785,7 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>81</v>
@@ -5637,16 +5794,16 @@
         <v>81</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5697,31 +5854,31 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>297</v>
+        <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>81</v>
+        <v>302</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>81</v>
@@ -5729,10 +5886,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5743,7 +5900,7 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>81</v>
@@ -5752,19 +5909,19 @@
         <v>81</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5814,31 +5971,31 @@
         <v>81</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>306</v>
+        <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>81</v>
@@ -5846,10 +6003,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5869,19 +6026,19 @@
         <v>81</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5931,7 +6088,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5943,19 +6100,19 @@
         <v>81</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>81</v>
+        <v>319</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>81</v>
@@ -5963,10 +6120,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5986,19 +6143,19 @@
         <v>81</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6048,7 +6205,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6060,19 +6217,19 @@
         <v>81</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>81</v>
+        <v>319</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>81</v>
@@ -6080,14 +6237,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6103,16 +6260,16 @@
         <v>81</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6163,7 +6320,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6175,19 +6332,19 @@
         <v>81</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>327</v>
+        <v>81</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>81</v>
+        <v>332</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>81</v>
@@ -6195,14 +6352,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6218,16 +6375,16 @@
         <v>81</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6278,7 +6435,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6290,19 +6447,19 @@
         <v>81</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>81</v>
+        <v>340</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>81</v>
@@ -6310,21 +6467,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>81</v>
@@ -6333,22 +6490,22 @@
         <v>81</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -6397,31 +6554,31 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>344</v>
+        <v>81</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>81</v>
+        <v>349</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>81</v>
@@ -6429,10 +6586,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6440,31 +6597,31 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6490,66 +6647,66 @@
         <v>81</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="AG37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6557,31 +6714,31 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6592,70 +6749,70 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="T38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X38" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y38" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>357</v>
-      </c>
       <c r="AG38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>132</v>
+        <v>369</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>365</v>
+        <v>135</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>81</v>
@@ -6663,10 +6820,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6686,22 +6843,22 @@
         <v>81</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6726,13 +6883,13 @@
         <v>81</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>81</v>
@@ -6750,7 +6907,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6762,19 +6919,19 @@
         <v>81</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>81</v>
@@ -6782,10 +6939,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6796,7 +6953,7 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>81</v>
@@ -6805,16 +6962,16 @@
         <v>81</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6822,7 +6979,7 @@
         <v>81</v>
       </c>
       <c r="Q40" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="R40" t="s" s="2">
         <v>81</v>
@@ -6843,55 +7000,55 @@
         <v>81</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="Z40" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>377</v>
-      </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>81</v>
@@ -6899,10 +7056,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6913,106 +7070,106 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q41" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="R41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="J41" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="P41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Q41" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="R41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>89</v>
-      </c>
       <c r="AI41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>394</v>
+        <v>81</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>81</v>
+        <v>398</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>81</v>
@@ -7020,21 +7177,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>81</v>
@@ -7043,19 +7200,19 @@
         <v>81</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>188</v>
+        <v>401</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7081,11 +7238,11 @@
         <v>81</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>81</v>
@@ -7103,42 +7260,42 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7149,7 +7306,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>81</v>
@@ -7161,13 +7318,13 @@
         <v>81</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7218,16 +7375,16 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>81</v>
@@ -7239,10 +7396,10 @@
         <v>81</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>81</v>
@@ -7250,14 +7407,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7276,16 +7433,16 @@
         <v>81</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7323,19 +7480,19 @@
         <v>81</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7347,7 +7504,7 @@
         <v>81</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>81</v>
@@ -7356,10 +7513,10 @@
         <v>81</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>81</v>
@@ -7367,10 +7524,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7381,7 +7538,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>81</v>
@@ -7390,23 +7547,19 @@
         <v>81</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>205</v>
+        <v>415</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>81</v>
       </c>
@@ -7454,31 +7607,31 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>209</v>
+        <v>417</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>210</v>
+        <v>81</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>211</v>
+        <v>81</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>81</v>
@@ -7486,10 +7639,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7500,7 +7653,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>81</v>
@@ -7509,23 +7662,19 @@
         <v>81</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>263</v>
+        <v>166</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>81</v>
       </c>
@@ -7534,7 +7683,7 @@
         <v>81</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>410</v>
+        <v>81</v>
       </c>
       <c r="T46" t="s" s="2">
         <v>81</v>
@@ -7573,31 +7722,31 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>268</v>
+        <v>168</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>81</v>
@@ -7605,14 +7754,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>412</v>
+        <v>137</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7628,19 +7777,19 @@
         <v>81</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>139</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>414</v>
+        <v>173</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>415</v>
+        <v>141</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7666,31 +7815,31 @@
         <v>81</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>416</v>
+        <v>81</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>417</v>
+        <v>81</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>81</v>
+        <v>174</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>176</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7699,25 +7848,25 @@
         <v>80</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>418</v>
+        <v>81</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>403</v>
+        <v>81</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>405</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" hidden="true">
@@ -7736,7 +7885,7 @@
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>81</v>
@@ -7745,20 +7894,22 @@
         <v>81</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>421</v>
+        <v>205</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>422</v>
+        <v>206</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>424</v>
+        <v>209</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7807,31 +7958,31 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>210</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>419</v>
+        <v>81</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>425</v>
+        <v>211</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>81</v>
+        <v>212</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>81</v>
@@ -7839,10 +7990,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7850,10 +8001,10 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>81</v>
@@ -7862,19 +8013,23 @@
         <v>81</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>427</v>
+        <v>229</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>428</v>
+        <v>266</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>269</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>81</v>
       </c>
@@ -7883,7 +8038,7 @@
         <v>81</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>81</v>
+        <v>422</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>81</v>
@@ -7922,53 +8077,53 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>426</v>
+        <v>271</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>431</v>
+        <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>432</v>
+        <v>272</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>433</v>
+        <v>273</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>434</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>436</v>
+        <v>81</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>81</v>
@@ -7977,16 +8132,16 @@
         <v>81</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8037,53 +8192,53 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>440</v>
+        <v>81</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>441</v>
+        <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>442</v>
+        <v>81</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>443</v>
+        <v>135</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>444</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>81</v>
@@ -8092,18 +8247,20 @@
         <v>81</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>81</v>
@@ -8140,83 +8297,83 @@
         <v>81</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AC51" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>81</v>
+      </c>
       <c r="AD51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>81</v>
+        <v>406</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>452</v>
+        <v>81</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>454</v>
+        <v>81</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>446</v>
+        <v>81</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>458</v>
+        <v>229</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>448</v>
+        <v>166</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>449</v>
+        <v>167</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8267,53 +8424,53 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>445</v>
+        <v>168</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>451</v>
+        <v>81</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>452</v>
+        <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>453</v>
+        <v>81</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>454</v>
+        <v>170</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>455</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>459</v>
+        <v>436</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>81</v>
@@ -8322,18 +8479,20 @@
         <v>81</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>460</v>
+        <v>138</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>461</v>
+        <v>139</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -8358,13 +8517,13 @@
         <v>81</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>463</v>
+        <v>81</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>464</v>
+        <v>81</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>81</v>
@@ -8382,19 +8541,19 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>459</v>
+        <v>176</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>81</v>
@@ -8403,53 +8562,57 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>465</v>
+        <v>81</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>81</v>
+        <v>170</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>466</v>
+        <v>81</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>468</v>
+        <v>438</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>458</v>
+        <v>138</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>469</v>
+        <v>439</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
       </c>
@@ -8497,53 +8660,53 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>471</v>
+        <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>472</v>
+        <v>81</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>473</v>
+        <v>81</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>474</v>
+        <v>135</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>475</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>476</v>
+        <v>442</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>476</v>
+        <v>442</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>477</v>
+        <v>81</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>81</v>
@@ -8552,20 +8715,18 @@
         <v>81</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>478</v>
+        <v>443</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>479</v>
+        <v>444</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>81</v>
@@ -8614,53 +8775,53 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>476</v>
+        <v>442</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>482</v>
+        <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>483</v>
+        <v>81</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>484</v>
+        <v>81</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>485</v>
+        <v>81</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>486</v>
+        <v>81</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>487</v>
+        <v>446</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>487</v>
+        <v>446</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>488</v>
+        <v>81</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>81</v>
@@ -8669,20 +8830,18 @@
         <v>81</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>188</v>
+        <v>430</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>489</v>
+        <v>447</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8707,13 +8866,13 @@
         <v>81</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>492</v>
+        <v>81</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>493</v>
+        <v>81</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>81</v>
@@ -8731,31 +8890,31 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>487</v>
+        <v>446</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>494</v>
+        <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>495</v>
+        <v>81</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>496</v>
+        <v>81</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>497</v>
+        <v>81</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>81</v>
@@ -8763,21 +8922,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>498</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>498</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>499</v>
+        <v>81</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>81</v>
@@ -8786,20 +8945,18 @@
         <v>81</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>500</v>
+        <v>229</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>501</v>
+        <v>166</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>503</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>81</v>
@@ -8848,31 +9005,31 @@
         <v>81</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>498</v>
+        <v>168</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>504</v>
+        <v>81</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>505</v>
+        <v>81</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>506</v>
+        <v>81</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>497</v>
+        <v>170</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>81</v>
@@ -8880,14 +9037,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>507</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>507</v>
+        <v>450</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>81</v>
+        <v>137</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8903,18 +9060,20 @@
         <v>81</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>508</v>
+        <v>139</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>81</v>
@@ -8939,13 +9098,13 @@
         <v>81</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>510</v>
+        <v>81</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>511</v>
+        <v>81</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>81</v>
@@ -8963,7 +9122,7 @@
         <v>81</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>507</v>
+        <v>176</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8975,7 +9134,7 @@
         <v>81</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>81</v>
@@ -8984,10 +9143,10 @@
         <v>81</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>512</v>
+        <v>81</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>497</v>
+        <v>170</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>81</v>
@@ -8995,14 +9154,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>513</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>513</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>81</v>
+        <v>438</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9015,22 +9174,26 @@
         <v>81</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>514</v>
+        <v>138</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>508</v>
+        <v>439</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>81</v>
       </c>
@@ -9078,7 +9241,7 @@
         <v>81</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>513</v>
+        <v>441</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9090,7 +9253,7 @@
         <v>81</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>81</v>
@@ -9099,10 +9262,10 @@
         <v>81</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>516</v>
+        <v>81</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>497</v>
+        <v>135</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>81</v>
@@ -9110,10 +9273,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>517</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>517</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9121,10 +9284,10 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>81</v>
@@ -9133,20 +9296,18 @@
         <v>81</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>518</v>
+        <v>453</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>520</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>81</v>
@@ -9171,11 +9332,13 @@
         <v>81</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>521</v>
+        <v>456</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>81</v>
@@ -9193,31 +9356,31 @@
         <v>81</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>517</v>
+        <v>452</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>522</v>
+        <v>81</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>523</v>
+        <v>81</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>524</v>
+        <v>81</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>525</v>
+        <v>81</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>81</v>
@@ -9225,10 +9388,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>526</v>
+        <v>457</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>526</v>
+        <v>457</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9236,10 +9399,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>81</v>
@@ -9248,18 +9411,20 @@
         <v>81</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>163</v>
+        <v>458</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>164</v>
+        <v>459</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>81</v>
@@ -9308,19 +9473,19 @@
         <v>81</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>166</v>
+        <v>457</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>81</v>
@@ -9329,7 +9494,7 @@
         <v>81</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>81</v>
@@ -9340,21 +9505,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>527</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>527</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>81</v>
@@ -9363,21 +9528,21 @@
         <v>81</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>463</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>136</v>
+        <v>464</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>81</v>
       </c>
@@ -9413,31 +9578,31 @@
         <v>81</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>171</v>
+        <v>81</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>172</v>
+        <v>81</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>173</v>
+        <v>81</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>174</v>
+        <v>462</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>81</v>
@@ -9446,10 +9611,10 @@
         <v>81</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>167</v>
+        <v>434</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>81</v>
+        <v>467</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>81</v>
@@ -9457,10 +9622,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>528</v>
+        <v>468</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9468,10 +9633,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>81</v>
@@ -9480,23 +9645,19 @@
         <v>81</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>204</v>
+        <v>469</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>205</v>
+        <v>470</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>81</v>
       </c>
@@ -9544,42 +9705,42 @@
         <v>81</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>209</v>
+        <v>468</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>81</v>
+        <v>472</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>210</v>
+        <v>473</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>211</v>
+        <v>474</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>81</v>
+        <v>475</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>81</v>
+        <v>476</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>529</v>
+        <v>477</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>529</v>
+        <v>477</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9590,7 +9751,7 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>81</v>
@@ -9599,23 +9760,19 @@
         <v>81</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>163</v>
+        <v>478</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>263</v>
+        <v>479</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>81</v>
       </c>
@@ -9624,7 +9781,7 @@
         <v>81</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>530</v>
+        <v>81</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>81</v>
@@ -9663,31 +9820,31 @@
         <v>81</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>268</v>
+        <v>477</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>269</v>
+        <v>473</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>81</v>
+        <v>481</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>81</v>
@@ -9695,21 +9852,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>531</v>
+        <v>482</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>531</v>
+        <v>482</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>81</v>
+        <v>483</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>81</v>
@@ -9718,20 +9875,18 @@
         <v>81</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>532</v>
+        <v>484</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>533</v>
+        <v>485</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>535</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>81</v>
@@ -9780,53 +9935,53 @@
         <v>81</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>531</v>
+        <v>482</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>536</v>
+        <v>487</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>537</v>
+        <v>488</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>538</v>
+        <v>489</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>525</v>
+        <v>490</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>81</v>
+        <v>491</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>539</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>539</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>81</v>
+        <v>493</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>81</v>
@@ -9835,16 +9990,16 @@
         <v>81</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>540</v>
+        <v>494</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>541</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>542</v>
+        <v>496</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9883,87 +10038,85 @@
         <v>81</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>81</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>539</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>543</v>
+        <v>498</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>544</v>
+        <v>499</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>545</v>
+        <v>500</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>546</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>504</v>
+      </c>
       <c r="D67" t="s" s="2">
-        <v>547</v>
+        <v>493</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>548</v>
+        <v>505</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>549</v>
+        <v>495</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>81</v>
@@ -10012,42 +10165,42 @@
         <v>81</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>546</v>
+        <v>492</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>552</v>
+        <v>498</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>553</v>
+        <v>499</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>554</v>
+        <v>500</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>81</v>
+        <v>501</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>81</v>
+        <v>502</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>555</v>
+        <v>506</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>555</v>
+        <v>506</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10055,10 +10208,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>81</v>
@@ -10067,20 +10220,18 @@
         <v>81</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>556</v>
+        <v>507</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>557</v>
+        <v>508</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>559</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>81</v>
@@ -10105,13 +10256,13 @@
         <v>81</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>81</v>
+        <v>510</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>81</v>
+        <v>511</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>81</v>
@@ -10129,53 +10280,53 @@
         <v>81</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>555</v>
+        <v>506</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>560</v>
+        <v>81</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>561</v>
+        <v>81</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>81</v>
+        <v>512</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>81</v>
+        <v>513</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>562</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>562</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>563</v>
+        <v>515</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>81</v>
@@ -10184,23 +10335,19 @@
         <v>81</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>188</v>
+        <v>505</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>564</v>
+        <v>516</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>81</v>
       </c>
@@ -10224,13 +10371,13 @@
         <v>81</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>372</v>
+        <v>81</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>568</v>
+        <v>81</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>569</v>
+        <v>81</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>81</v>
@@ -10248,73 +10395,75 @@
         <v>81</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>562</v>
+        <v>514</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>81</v>
+        <v>518</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>560</v>
+        <v>519</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>81</v>
+        <v>521</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>571</v>
+        <v>522</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>572</v>
+        <v>523</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>572</v>
+        <v>523</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>81</v>
+        <v>524</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>573</v>
+        <v>525</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>50</v>
+        <v>526</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>81</v>
@@ -10363,53 +10512,53 @@
         <v>81</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>572</v>
+        <v>523</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>575</v>
+        <v>529</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>419</v>
+        <v>530</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>576</v>
+        <v>531</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>81</v>
+        <v>532</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>577</v>
+        <v>533</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>578</v>
+        <v>534</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>578</v>
+        <v>534</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>81</v>
+        <v>535</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>81</v>
@@ -10418,18 +10567,20 @@
         <v>81</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>163</v>
+        <v>189</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>579</v>
+        <v>536</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>81</v>
@@ -10454,13 +10605,13 @@
         <v>81</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>81</v>
+        <v>376</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>81</v>
+        <v>539</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>81</v>
+        <v>540</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>81</v>
@@ -10478,31 +10629,31 @@
         <v>81</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>578</v>
+        <v>534</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>81</v>
+        <v>541</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>419</v>
+        <v>542</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>581</v>
+        <v>543</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>81</v>
+        <v>544</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>81</v>
@@ -10510,21 +10661,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>582</v>
+        <v>545</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>582</v>
+        <v>545</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>81</v>
+        <v>546</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>81</v>
@@ -10533,19 +10684,19 @@
         <v>81</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>583</v>
+        <v>547</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>584</v>
+        <v>548</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>585</v>
+        <v>549</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>586</v>
+        <v>550</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10595,7 +10746,7 @@
         <v>81</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>582</v>
+        <v>545</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10607,26 +10758,1656 @@
         <v>81</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AL72" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO76" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="AN72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AO72" t="s" s="2">
+      <c r="B77" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO72">
+  <autoFilter ref="A1:AO86">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10636,7 +12417,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI71">
+  <conditionalFormatting sqref="A2:AI85">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-HIV-lab-order.xlsx
+++ b/branches/master/StructureDefinition-HIV-lab-order.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
